--- a/Data Repository/Configuration/Tax_Classification.xlsx
+++ b/Data Repository/Configuration/Tax_Classification.xlsx
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
